--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$30</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="232">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T08:57:08+00:00</t>
+    <t>2026-02-23T17:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>**Beschreibung:** Timing</t>
+    <t>**Beschreibung:** ELGA e-Med Timing</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -362,7 +365,7 @@
 </t>
   </si>
   <si>
-    <t>When the event occurs</t>
+    <t>Zeitpunkt der Einnahme: Mapping /effectiveTime[1]/@value</t>
   </si>
   <si>
     <t>Identifies specific times when the event occurs.</t>
@@ -381,7 +384,7 @@
 </t>
   </si>
   <si>
-    <t>When the event is to occur</t>
+    <t>Wiederholungsangaben zur Einnahme</t>
   </si>
   <si>
     <t>A set of rules that describe when the event is scheduled.</t>
@@ -416,7 +419,88 @@
     <t>Either a duration for the length of the timing schedule, a range of possible length, or outer bounds for start and/or end limits of the timing schedule.</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
     <t>IVL(TS) used in a QSI</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x]:boundsPeriod</t>
+  </si>
+  <si>
+    <t>boundsPeriod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x]:boundsPeriod.id</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x].id</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x]:boundsPeriod.extension</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x].extension</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x]:boundsPeriod.start</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x].start</t>
+  </si>
+  <si>
+    <t>Zeitraum der Einnahme: Start. Mapping /effectiveTime[1]/low</t>
+  </si>
+  <si>
+    <t>The start of the period. The boundary is inclusive.</t>
+  </si>
+  <si>
+    <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
+  </si>
+  <si>
+    <t>Period.start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per-1
+</t>
+  </si>
+  <si>
+    <t>DR.1</t>
+  </si>
+  <si>
+    <t>./low</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x]:boundsPeriod.end</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x].end</t>
+  </si>
+  <si>
+    <t>Zeitraum der Einnahme: Ende. Mapping /effectiveTime[1]/high</t>
+  </si>
+  <si>
+    <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
+  </si>
+  <si>
+    <t>The high value includes any matching date/time. i.e. 2012-02-03T10:00:00 is in a period that has an end value of 2012-02-03.</t>
+  </si>
+  <si>
+    <t>If the end of the period is missing, it means that the period is ongoing</t>
+  </si>
+  <si>
+    <t>Period.end</t>
+  </si>
+  <si>
+    <t>DR.2</t>
+  </si>
+  <si>
+    <t>./high</t>
   </si>
   <si>
     <t>Timing.repeat.count</t>
@@ -509,7 +593,8 @@
     <t>Timing.repeat.frequency</t>
   </si>
   <si>
-    <t>Event occurs frequency times per period</t>
+    <t>Häufigkeit der Einnahme, z.B. 1 mal täglich.
+Periodic Frequency /effectiveTime[operator="A" and xsi:type="PIVL_TS"] …/@institutionSpecified …/period/@value …/period/@unit</t>
   </si>
   <si>
     <t>The number of times to repeat the action within the specified period. If frequencyMax is present, this element indicates the lower bound of the allowed range of the frequency.</t>
@@ -530,6 +615,9 @@
     <t>Timing.repeat.period</t>
   </si>
   <si>
+    <t>Intervall der Einnahme, z.B. alle 8 Stunden.</t>
+  </si>
+  <si>
     <t>Indicates the duration of time over which repetitions are to occur; e.g. to express "3 times per day", 3 would be the frequency and "1 day" would be the period. If periodMax is present, this element indicates the lower bound of the allowed range of the period length.</t>
   </si>
   <si>
@@ -545,7 +633,13 @@
     <t>Timing.repeat.periodUnit</t>
   </si>
   <si>
+    <t>Einheit des Intervalls der Einnahme, z.B. h für Stunden, d für Tage.</t>
+  </si>
+  <si>
     <t>The units of time for the period in UCUM units.</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/ValueSet/elga-medikationfrequenz</t>
   </si>
   <si>
     <t>Timing.repeat.dayOfWeek</t>
@@ -594,10 +688,7 @@
     <t>Timings are frequently determined by occurrences such as waking, eating and sleep.</t>
   </si>
   <si>
-    <t>Real world event relating to the schedule.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/event-timing|4.0.1</t>
+    <t>https://termgit.elga.gv.at/ValueSet/elga-einnahmezeitpunkte</t>
   </si>
   <si>
     <t>EIVL.event</t>
@@ -773,6 +864,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -954,12 +1060,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL25"/>
+  <dimension ref="A1:AL30"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="23.578125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="23.578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="1" max="1" width="39.78125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="28.5234375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.62109375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -982,7 +1088,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="34.453125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="42.51171875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.90234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -1112,7 +1218,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -1220,7 +1326,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>85</v>
       </c>
@@ -1326,7 +1432,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>92</v>
       </c>
@@ -1434,7 +1540,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>103</v>
       </c>
@@ -1563,7 +1669,7 @@
         <v>77</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="I6" t="s" s="2">
         <v>21</v>
@@ -1671,7 +1777,7 @@
         <v>86</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>21</v>
@@ -1760,7 +1866,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>123</v>
       </c>
@@ -1866,7 +1972,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>124</v>
       </c>
@@ -1974,7 +2080,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>125</v>
       </c>
@@ -2047,16 +2153,14 @@
         <v>21</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC10" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="AC10" s="2"/>
       <c r="AD10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AF10" t="s" s="2">
         <v>125</v>
@@ -2077,17 +2181,19 @@
         <v>21</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>125</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>132</v>
+      </c>
       <c r="D11" t="s" s="2">
         <v>21</v>
       </c>
@@ -2108,20 +2214,16 @@
         <v>105</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>135</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>21</v>
       </c>
@@ -2169,7 +2271,7 @@
         <v>21</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>76</v>
@@ -2187,15 +2289,15 @@
         <v>21</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2215,16 +2317,16 @@
         <v>21</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>131</v>
+        <v>87</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>138</v>
+        <v>88</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>139</v>
+        <v>89</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2275,7 +2377,7 @@
         <v>21</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -2287,32 +2389,32 @@
         <v>21</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL12" t="s" s="2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" hidden="true">
+      <c r="A13" t="s" s="2">
         <v>136</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>140</v>
-      </c>
       <c r="B13" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>21</v>
@@ -2321,23 +2423,21 @@
         <v>21</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>141</v>
+        <v>94</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>142</v>
+        <v>95</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>143</v>
+        <v>96</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>21</v>
       </c>
@@ -2373,45 +2473,45 @@
         <v>21</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2434,20 +2534,18 @@
         <v>105</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="L14" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>149</v>
-      </c>
       <c r="N14" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>21</v>
       </c>
@@ -2495,7 +2593,7 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -2504,24 +2602,24 @@
         <v>86</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>21</v>
+        <v>145</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>146</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2544,20 +2642,24 @@
         <v>105</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="L15" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q15" s="2"/>
+      <c r="Q15" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="R15" t="s" s="2">
         <v>21</v>
       </c>
@@ -2577,13 +2679,13 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>155</v>
+        <v>21</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -2601,7 +2703,7 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -2610,24 +2712,24 @@
         <v>86</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2650,22 +2752,24 @@
         <v>105</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
+      <c r="O16" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q16" t="s" s="2">
-        <v>161</v>
-      </c>
+      <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
         <v>21</v>
       </c>
@@ -2709,7 +2813,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -2727,15 +2831,15 @@
         <v>21</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2758,13 +2862,13 @@
         <v>105</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2815,7 +2919,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -2833,15 +2937,15 @@
         <v>21</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2864,16 +2968,20 @@
         <v>105</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>21</v>
       </c>
@@ -2921,7 +3029,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -2939,15 +3047,15 @@
         <v>21</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2970,16 +3078,20 @@
         <v>105</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>21</v>
       </c>
@@ -3027,7 +3139,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -3045,15 +3157,15 @@
         <v>21</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3076,13 +3188,13 @@
         <v>105</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3109,13 +3221,13 @@
         <v>21</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>154</v>
+        <v>180</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>156</v>
+        <v>182</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>21</v>
@@ -3133,7 +3245,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -3151,15 +3263,15 @@
         <v>21</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3170,7 +3282,7 @@
         <v>76</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>21</v>
@@ -3182,22 +3294,22 @@
         <v>105</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>175</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q21" s="2"/>
+      <c r="Q21" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="R21" t="s" s="2">
         <v>21</v>
       </c>
@@ -3217,11 +3329,13 @@
         <v>21</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="Y21" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z21" t="s" s="2">
-        <v>176</v>
+        <v>21</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>21</v>
@@ -3239,13 +3353,13 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>21</v>
@@ -3257,15 +3371,15 @@
         <v>21</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3276,7 +3390,7 @@
         <v>76</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>21</v>
@@ -3288,17 +3402,15 @@
         <v>105</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>181</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -3347,13 +3459,13 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>21</v>
@@ -3365,15 +3477,15 @@
         <v>21</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>91</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3384,10 +3496,10 @@
         <v>76</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>21</v>
@@ -3396,20 +3508,16 @@
         <v>105</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>186</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>21</v>
       </c>
@@ -3433,13 +3541,13 @@
         <v>21</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>188</v>
+        <v>21</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>21</v>
@@ -3457,13 +3565,13 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>21</v>
@@ -3475,15 +3583,15 @@
         <v>21</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3506,13 +3614,13 @@
         <v>105</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>191</v>
+        <v>167</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3563,7 +3671,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -3581,15 +3689,15 @@
         <v>21</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3612,17 +3720,15 @@
         <v>105</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N25" t="s" s="2">
         <v>199</v>
       </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>21</v>
@@ -3647,14 +3753,12 @@
         <v>21</v>
       </c>
       <c r="X25" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="Y25" s="2"/>
+      <c r="Z25" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="Y25" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>202</v>
-      </c>
       <c r="AA25" t="s" s="2">
         <v>21</v>
       </c>
@@ -3671,7 +3775,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -3689,10 +3793,564 @@
         <v>21</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="26" hidden="true">
+      <c r="A26" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="K26" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>203</v>
       </c>
+      <c r="N26" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="O26" s="2"/>
+      <c r="P26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q26" s="2"/>
+      <c r="R26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="Y26" s="2"/>
+      <c r="Z26" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="27" hidden="true">
+      <c r="A27" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="K27" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="O27" s="2"/>
+      <c r="P27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q27" s="2"/>
+      <c r="R27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="P28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q28" s="2"/>
+      <c r="R28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="Y28" s="2"/>
+      <c r="Z28" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q29" s="2"/>
+      <c r="R29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="30" hidden="true">
+      <c r="A30" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="O30" s="2"/>
+      <c r="P30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q30" s="2"/>
+      <c r="R30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>231</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AL30">
+    <filterColumn colId="7">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="27">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI29">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="231">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T17:25:44+00:00</t>
+    <t>2026-02-26T16:36:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -85,9 +85,6 @@
   </si>
   <si>
     <t>Description</t>
-  </si>
-  <si>
-    <t>**Beschreibung:** ELGA e-Med Timing</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -990,67 +987,67 @@
         <v>22</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>26</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>27</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>28</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>29</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>30</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>31</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>32</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>34</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>35</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>36</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1104,126 +1101,126 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="B1" t="s" s="1">
         <v>38</v>
       </c>
-      <c r="B1" t="s" s="1">
+      <c r="C1" t="s" s="1">
         <v>39</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="D1" t="s" s="1">
         <v>40</v>
       </c>
-      <c r="D1" t="s" s="1">
+      <c r="E1" t="s" s="1">
         <v>41</v>
       </c>
-      <c r="E1" t="s" s="1">
+      <c r="F1" t="s" s="1">
         <v>42</v>
       </c>
-      <c r="F1" t="s" s="1">
+      <c r="G1" t="s" s="1">
         <v>43</v>
       </c>
-      <c r="G1" t="s" s="1">
+      <c r="H1" t="s" s="1">
         <v>44</v>
       </c>
-      <c r="H1" t="s" s="1">
+      <c r="I1" t="s" s="1">
         <v>45</v>
       </c>
-      <c r="I1" t="s" s="1">
+      <c r="J1" t="s" s="1">
         <v>46</v>
       </c>
-      <c r="J1" t="s" s="1">
+      <c r="K1" t="s" s="1">
         <v>47</v>
       </c>
-      <c r="K1" t="s" s="1">
+      <c r="L1" t="s" s="1">
         <v>48</v>
       </c>
-      <c r="L1" t="s" s="1">
+      <c r="M1" t="s" s="1">
         <v>49</v>
       </c>
-      <c r="M1" t="s" s="1">
+      <c r="N1" t="s" s="1">
         <v>50</v>
       </c>
-      <c r="N1" t="s" s="1">
+      <c r="O1" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="O1" t="s" s="1">
+      <c r="P1" t="s" s="1">
         <v>52</v>
       </c>
-      <c r="P1" t="s" s="1">
+      <c r="Q1" t="s" s="1">
         <v>53</v>
       </c>
-      <c r="Q1" t="s" s="1">
+      <c r="R1" t="s" s="1">
         <v>54</v>
       </c>
-      <c r="R1" t="s" s="1">
+      <c r="S1" t="s" s="1">
         <v>55</v>
       </c>
-      <c r="S1" t="s" s="1">
+      <c r="T1" t="s" s="1">
         <v>56</v>
       </c>
-      <c r="T1" t="s" s="1">
+      <c r="U1" t="s" s="1">
         <v>57</v>
       </c>
-      <c r="U1" t="s" s="1">
+      <c r="V1" t="s" s="1">
         <v>58</v>
       </c>
-      <c r="V1" t="s" s="1">
+      <c r="W1" t="s" s="1">
         <v>59</v>
       </c>
-      <c r="W1" t="s" s="1">
+      <c r="X1" t="s" s="1">
         <v>60</v>
       </c>
-      <c r="X1" t="s" s="1">
+      <c r="Y1" t="s" s="1">
         <v>61</v>
       </c>
-      <c r="Y1" t="s" s="1">
+      <c r="Z1" t="s" s="1">
         <v>62</v>
       </c>
-      <c r="Z1" t="s" s="1">
+      <c r="AA1" t="s" s="1">
         <v>63</v>
       </c>
-      <c r="AA1" t="s" s="1">
+      <c r="AB1" t="s" s="1">
         <v>64</v>
       </c>
-      <c r="AB1" t="s" s="1">
+      <c r="AC1" t="s" s="1">
         <v>65</v>
       </c>
-      <c r="AC1" t="s" s="1">
+      <c r="AD1" t="s" s="1">
         <v>66</v>
       </c>
-      <c r="AD1" t="s" s="1">
+      <c r="AE1" t="s" s="1">
         <v>67</v>
       </c>
-      <c r="AE1" t="s" s="1">
+      <c r="AF1" t="s" s="1">
         <v>68</v>
       </c>
-      <c r="AF1" t="s" s="1">
+      <c r="AG1" t="s" s="1">
         <v>69</v>
       </c>
-      <c r="AG1" t="s" s="1">
+      <c r="AH1" t="s" s="1">
         <v>70</v>
       </c>
-      <c r="AH1" t="s" s="1">
+      <c r="AI1" t="s" s="1">
         <v>71</v>
       </c>
-      <c r="AI1" t="s" s="1">
+      <c r="AJ1" t="s" s="1">
         <v>72</v>
       </c>
-      <c r="AJ1" t="s" s="1">
+      <c r="AK1" t="s" s="1">
         <v>73</v>
       </c>
-      <c r="AK1" t="s" s="1">
+      <c r="AL1" t="s" s="1">
         <v>74</v>
-      </c>
-      <c r="AL1" t="s" s="1">
-        <v>75</v>
       </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -1231,31 +1228,31 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G2" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="G2" t="s" s="2">
+      <c r="H2" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I2" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="H2" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I2" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J2" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K2" t="s" s="2">
+      <c r="L2" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="L2" t="s" s="2">
+      <c r="M2" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="M2" t="s" s="2">
+      <c r="N2" t="s" s="2">
         <v>80</v>
-      </c>
-      <c r="N2" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
@@ -1305,33 +1302,33 @@
         <v>21</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH2" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="AH2" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AI2" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ2" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK2" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AK2" t="s" s="2">
+      <c r="AL2" t="s" s="2">
         <v>83</v>
-      </c>
-      <c r="AL2" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1339,28 +1336,28 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="M3" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1411,45 +1408,45 @@
         <v>21</v>
       </c>
       <c r="AF3" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH3" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI3" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ3" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK3" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL3" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="AG3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH3" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI3" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ3" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK3" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL3" t="s" s="2">
-        <v>91</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G4" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="G4" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="H4" t="s" s="2">
         <v>21</v>
       </c>
@@ -1460,16 +1457,16 @@
         <v>21</v>
       </c>
       <c r="K4" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="M4" t="s" s="2">
+      <c r="N4" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="N4" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
@@ -1507,80 +1504,80 @@
         <v>21</v>
       </c>
       <c r="AB4" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AC4" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="AC4" t="s" s="2">
+      <c r="AD4" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE4" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AD4" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE4" t="s" s="2">
+      <c r="AF4" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AF4" t="s" s="2">
+      <c r="AG4" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AG4" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>102</v>
-      </c>
       <c r="AK4" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G5" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="G5" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="H5" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I5" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="J5" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="K5" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="J5" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="K5" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="O5" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="O5" t="s" s="2">
-        <v>108</v>
       </c>
       <c r="P5" t="s" s="2">
         <v>21</v>
@@ -1629,33 +1626,33 @@
         <v>21</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH5" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="AH5" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AI5" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1663,32 +1660,32 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G6" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="G6" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="H6" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P6" t="s" s="2">
         <v>21</v>
@@ -1737,33 +1734,33 @@
         <v>21</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AG6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH6" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="AH6" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AI6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1771,32 +1768,32 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>118</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P7" t="s" s="2">
         <v>21</v>
@@ -1845,33 +1842,33 @@
         <v>21</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ7" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL7" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>122</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1879,28 +1876,28 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K8" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K8" t="s" s="2">
+      <c r="L8" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1951,45 +1948,45 @@
         <v>21</v>
       </c>
       <c r="AF8" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL8" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="AG8" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL8" t="s" s="2">
-        <v>91</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G9" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="G9" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="H9" t="s" s="2">
         <v>21</v>
       </c>
@@ -2000,16 +1997,16 @@
         <v>21</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2047,45 +2044,45 @@
         <v>21</v>
       </c>
       <c r="AB9" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AC9" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="AC9" t="s" s="2">
+      <c r="AD9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE9" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AD9" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE9" t="s" s="2">
+      <c r="AF9" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AF9" t="s" s="2">
+      <c r="AG9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ9" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AG9" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH9" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI9" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ9" t="s" s="2">
-        <v>102</v>
-      </c>
       <c r="AK9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2093,10 +2090,10 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>21</v>
@@ -2105,16 +2102,16 @@
         <v>21</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="L10" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="M10" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2153,56 +2150,56 @@
         <v>21</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AC10" s="2"/>
       <c r="AD10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="C11" t="s" s="2">
         <v>131</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>132</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>21</v>
@@ -2211,16 +2208,16 @@
         <v>21</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2271,33 +2268,33 @@
         <v>21</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>135</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2305,28 +2302,28 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K12" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K12" t="s" s="2">
+      <c r="L12" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2377,45 +2374,45 @@
         <v>21</v>
       </c>
       <c r="AF12" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL12" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>91</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>137</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G13" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="G13" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="H13" t="s" s="2">
         <v>21</v>
       </c>
@@ -2426,16 +2423,16 @@
         <v>21</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2473,45 +2470,45 @@
         <v>21</v>
       </c>
       <c r="AB13" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AC13" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="AC13" t="s" s="2">
+      <c r="AD13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE13" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AD13" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE13" t="s" s="2">
+      <c r="AF13" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AF13" t="s" s="2">
+      <c r="AG13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AG13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>102</v>
-      </c>
       <c r="AK13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>139</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2519,10 +2516,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>21</v>
@@ -2531,19 +2528,19 @@
         <v>21</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2593,33 +2590,33 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI14" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="AG14" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI14" t="s" s="2">
+      <c r="AJ14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK14" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="AJ14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK14" t="s" s="2">
+      <c r="AL14" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>146</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>148</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2627,10 +2624,10 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>21</v>
@@ -2639,97 +2636,97 @@
         <v>21</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q15" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="R15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="R15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF15" t="s" s="2">
+      <c r="AG15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK15" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AG15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI15" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK15" t="s" s="2">
+      <c r="AL15" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>155</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2737,10 +2734,10 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>21</v>
@@ -2749,22 +2746,22 @@
         <v>21</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>21</v>
@@ -2813,33 +2810,33 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2847,10 +2844,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>21</v>
@@ -2859,16 +2856,16 @@
         <v>21</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2919,33 +2916,33 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2953,10 +2950,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>21</v>
@@ -2965,22 +2962,22 @@
         <v>21</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>21</v>
@@ -3029,33 +3026,33 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3063,10 +3060,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>21</v>
@@ -3075,22 +3072,22 @@
         <v>21</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="M19" t="s" s="2">
-        <v>175</v>
-      </c>
       <c r="N19" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="O19" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -3139,33 +3136,33 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3173,10 +3170,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>21</v>
@@ -3185,16 +3182,16 @@
         <v>21</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3221,57 +3218,57 @@
         <v>21</v>
       </c>
       <c r="X20" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="Y20" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="Y20" t="s" s="2">
+      <c r="Z20" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="Z20" t="s" s="2">
+      <c r="AA20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL20" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>183</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3279,10 +3276,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>21</v>
@@ -3291,16 +3288,16 @@
         <v>21</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3308,7 +3305,7 @@
         <v>21</v>
       </c>
       <c r="Q21" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R21" t="s" s="2">
         <v>21</v>
@@ -3353,33 +3350,33 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3387,10 +3384,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>21</v>
@@ -3399,16 +3396,16 @@
         <v>21</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>190</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3459,33 +3456,33 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3493,28 +3490,28 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3565,33 +3562,33 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3599,10 +3596,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>21</v>
@@ -3611,16 +3608,16 @@
         <v>21</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3671,33 +3668,33 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3705,10 +3702,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>21</v>
@@ -3717,16 +3714,16 @@
         <v>21</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3753,11 +3750,11 @@
         <v>21</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>21</v>
@@ -3775,33 +3772,33 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3809,11 +3806,11 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G26" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="G26" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="H26" t="s" s="2">
         <v>21</v>
       </c>
@@ -3821,19 +3818,19 @@
         <v>21</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -3859,11 +3856,11 @@
         <v>21</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -3881,33 +3878,33 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AG26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH26" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="AH26" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AI26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3915,11 +3912,11 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G27" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="G27" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="H27" t="s" s="2">
         <v>21</v>
       </c>
@@ -3927,19 +3924,19 @@
         <v>21</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -3989,33 +3986,33 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AG27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH27" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="AH27" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AI27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4023,34 +4020,34 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G28" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="G28" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="H28" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -4075,55 +4072,55 @@
         <v>21</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="AG28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>217</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4131,28 +4128,28 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4203,33 +4200,33 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4237,10 +4234,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>21</v>
@@ -4249,19 +4246,19 @@
         <v>21</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4287,49 +4284,49 @@
         <v>21</v>
       </c>
       <c r="X30" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="Y30" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="Y30" t="s" s="2">
+      <c r="Z30" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="Z30" t="s" s="2">
+      <c r="AA30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="AG30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>231</v>
       </c>
     </row>
   </sheetData>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T16:36:39+00:00</t>
+    <t>2026-03-03T08:59:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T08:59:33+00:00</t>
+    <t>2026-03-03T14:03:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T14:03:22+00:00</t>
+    <t>2026-03-05T12:55:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T12:55:37+00:00</t>
+    <t>2026-03-05T13:31:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T13:31:59+00:00</t>
+    <t>2026-03-06T12:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T12:22:28+00:00</t>
+    <t>2026-03-06T14:18:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T14:18:10+00:00</t>
+    <t>2026-03-09T08:14:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T08:14:04+00:00</t>
+    <t>2026-03-09T10:03:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T10:03:26+00:00</t>
+    <t>2026-03-09T11:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T11:27:52+00:00</t>
+    <t>2026-03-10T08:28:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T08:28:41+00:00</t>
+    <t>2026-03-10T11:00:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T11:00:19+00:00</t>
+    <t>2026-03-10T11:31:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T11:31:06+00:00</t>
+    <t>2026-03-16T16:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T16:50:24+00:00</t>
+    <t>2026-03-19T16:44:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T16:44:44+00:00</t>
+    <t>2026-03-20T13:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T13:50:58+00:00</t>
+    <t>2026-03-20T15:30:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T15:30:14+00:00</t>
+    <t>2026-03-24T10:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T10:00:40+00:00</t>
+    <t>2026-03-24T15:12:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T15:12:36+00:00</t>
+    <t>2026-03-27T10:18:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T10:18:57+00:00</t>
+    <t>2026-03-30T07:39:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T07:39:16+00:00</t>
+    <t>2026-03-30T10:13:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T10:13:35+00:00</t>
+    <t>2026-04-01T13:59:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T13:59:59+00:00</t>
+    <t>2026-04-02T15:01:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T15:01:02+00:00</t>
+    <t>2026-04-07T09:06:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T09:06:22+00:00</t>
+    <t>2026-04-07T15:41:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T15:41:53+00:00</t>
+    <t>2026-04-07T16:09:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T16:09:01+00:00</t>
+    <t>2026-04-08T18:33:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T18:33:44+00:00</t>
+    <t>2026-04-09T06:40:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T06:40:16+00:00</t>
+    <t>2026-04-09T18:30:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T18:30:31+00:00</t>
+    <t>2026-04-10T11:48:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T11:48:51+00:00</t>
+    <t>2026-04-13T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T14:44:53+00:00</t>
+    <t>2026-04-13T15:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T15:27:52+00:00</t>
+    <t>2026-04-13T20:12:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T20:12:42+00:00</t>
+    <t>2026-04-14T10:13:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T10:13:14+00:00</t>
+    <t>2026-04-17T19:15:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T19:15:07+00:00</t>
+    <t>2026-04-20T08:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T08:20:06+00:00</t>
+    <t>2026-04-20T16:24:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T16:24:35+00:00</t>
+    <t>2026-04-20T19:04:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -362,7 +362,7 @@
 </t>
   </si>
   <si>
-    <t>Zeitpunkt der Einnahme: Mapping /effectiveTime[1]/@value</t>
+    <t>Zeitpunkt der Einnahme.</t>
   </si>
   <si>
     <t>Identifies specific times when the event occurs.</t>
@@ -451,7 +451,7 @@
     <t>Timing.repeat.bounds[x].start</t>
   </si>
   <si>
-    <t>Zeitraum der Einnahme: Start. Mapping /effectiveTime[1]/low</t>
+    <t>Zeitraum der Einnahme: Start.</t>
   </si>
   <si>
     <t>The start of the period. The boundary is inclusive.</t>
@@ -479,7 +479,7 @@
     <t>Timing.repeat.bounds[x].end</t>
   </si>
   <si>
-    <t>Zeitraum der Einnahme: Ende. Mapping /effectiveTime[1]/high</t>
+    <t>Zeitraum der Einnahme: Ende.</t>
   </si>
   <si>
     <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
@@ -590,8 +590,7 @@
     <t>Timing.repeat.frequency</t>
   </si>
   <si>
-    <t>Häufigkeit der Einnahme, z.B. 1 mal täglich.
-Periodic Frequency /effectiveTime[operator="A" and xsi:type="PIVL_TS"] …/@institutionSpecified …/period/@value …/period/@unit</t>
+    <t>Häufigkeit der Einnahme, z.B. 3 mal täglich.</t>
   </si>
   <si>
     <t>The number of times to repeat the action within the specified period. If frequencyMax is present, this element indicates the lower bound of the allowed range of the frequency.</t>
@@ -612,7 +611,7 @@
     <t>Timing.repeat.period</t>
   </si>
   <si>
-    <t>Intervall der Einnahme, z.B. alle 8 Stunden.</t>
+    <t>Intervall der Einnahme, z.B. alle 4 Stunden.</t>
   </si>
   <si>
     <t>Indicates the duration of time over which repetitions are to occur; e.g. to express "3 times per day", 3 would be the frequency and "1 day" would be the period. If periodMax is present, this element indicates the lower bound of the allowed range of the period length.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T19:04:12+00:00</t>
+    <t>2026-04-21T08:44:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T08:44:51+00:00</t>
+    <t>2026-04-21T11:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T11:54:48+00:00</t>
+    <t>2026-04-21T14:09:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T14:09:10+00:00</t>
+    <t>2026-04-21T17:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T17:01:26+00:00</t>
+    <t>2026-04-22T08:49:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T08:49:17+00:00</t>
+    <t>2026-04-22T10:01:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T10:01:54+00:00</t>
+    <t>2026-04-22T10:11:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T10:11:27+00:00</t>
+    <t>2026-04-28T11:58:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-28T11:58:02+00:00</t>
+    <t>2026-04-29T14:27:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T14:27:58+00:00</t>
+    <t>2026-04-30T15:16:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T15:16:21+00:00</t>
+    <t>2026-04-30T15:23:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T15:23:35+00:00</t>
+    <t>2026-05-04T14:46:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:46:25+00:00</t>
+    <t>2026-05-08T13:20:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
